--- a/astro-site/public/dl/kit-tareas-cafeteria/04-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas-cafeteria/04-tareas-perfiles.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Encargado" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Barista" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Pastelero" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Camarero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Auxiliar" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Encargado" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Barista" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pastelero" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camarero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auxiliar" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Encargado'!$A$1:$G$27</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Barista'!$A$1:$G$32</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pastelero'!$A$1:$G$27</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Camarero'!$A$1:$G$28</definedName>
-    <definedName localSheetId="5" name="_xlnm.Print_Area">'Auxiliar'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Encargado'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Barista'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Pastelero'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Camarero'!$A$1:$G$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Auxiliar'!$A$1:$G$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,6 +87,11 @@
       <color rgb="00888888"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -144,50 +149,66 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -547,15 +568,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B10"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -563,6 +585,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -570,6 +593,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -591,6 +615,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -598,8 +623,33 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-cafeteria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -613,16 +663,16 @@
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Tareas Diarias — Encargado/a de Cafetería</t>
@@ -636,10 +686,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -664,7 +715,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -681,10 +732,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -710,10 +759,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -739,10 +786,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -768,10 +813,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -797,10 +840,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -833,10 +874,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -862,10 +901,8 @@
       <c r="G12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
@@ -891,10 +928,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -920,10 +955,8 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -956,10 +989,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
@@ -985,10 +1016,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -1014,10 +1043,8 @@
       <c r="G18" s="11" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
@@ -1043,10 +1070,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="20" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -1072,10 +1097,8 @@
       <c r="G20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
@@ -1100,6 +1123,7 @@
       <c r="F21" s="15" t="n"/>
       <c r="G21" s="15" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="C23" s="16" t="inlineStr">
         <is>
@@ -1108,14 +1132,19 @@
       </c>
       <c r="D23" s="17">
         <f>COUNTIF(F5:F21,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>de 14</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F23">
+        <f>COUNTIF(B5:B21,"?*")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
@@ -1123,6 +1152,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
@@ -1140,8 +1170,18 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G21">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1155,16 +1195,16 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Tareas Diarias — Barista</t>
@@ -1178,10 +1218,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1206,7 +1247,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1223,10 +1264,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -1252,10 +1291,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -1281,10 +1318,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -1310,10 +1345,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -1339,10 +1372,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -1368,10 +1399,8 @@
       <c r="G10" s="11" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="21" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
@@ -1397,10 +1426,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -1433,10 +1460,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -1462,10 +1487,8 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -1491,10 +1514,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -1520,10 +1541,8 @@
       <c r="G16" s="11" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>11</v>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
@@ -1549,10 +1568,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>12</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -1578,10 +1595,8 @@
       <c r="G18" s="11" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="21" t="n">
+        <v>13</v>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
@@ -1614,10 +1629,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
@@ -1643,10 +1656,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="20" t="n">
+        <v>15</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
@@ -1672,10 +1683,8 @@
       <c r="G22" s="11" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="21" t="n">
+        <v>16</v>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
@@ -1701,10 +1710,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="20" t="n">
+        <v>17</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -1730,10 +1737,8 @@
       <c r="G24" s="11" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="21" t="n">
+        <v>18</v>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
@@ -1759,10 +1764,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="20" t="n">
+        <v>19</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
@@ -1787,6 +1790,7 @@
       <c r="F26" s="11" t="n"/>
       <c r="G26" s="11" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="C28" s="16" t="inlineStr">
         <is>
@@ -1795,14 +1799,19 @@
       </c>
       <c r="D28" s="17">
         <f>COUNTIF(F5:F26,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>de 19</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F28">
+        <f>COUNTIF(B5:B26,"?*")</f>
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
@@ -1810,6 +1819,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
@@ -1823,12 +1833,22 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G26">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F14 F15 F16 F17 F18 F19 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1842,16 +1862,16 @@
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Tareas Diarias — Pastelero/a</t>
@@ -1865,10 +1885,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1893,7 +1914,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1910,10 +1931,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -1939,10 +1958,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -1968,10 +1985,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -1997,10 +2012,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -2033,10 +2046,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
@@ -2062,10 +2073,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -2091,10 +2100,8 @@
       <c r="G12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
@@ -2120,10 +2127,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -2149,10 +2154,8 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -2185,10 +2188,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
@@ -2214,10 +2215,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -2243,10 +2242,8 @@
       <c r="G18" s="11" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
@@ -2272,10 +2269,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="20" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -2301,10 +2296,8 @@
       <c r="G20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
@@ -2329,6 +2322,7 @@
       <c r="F21" s="15" t="n"/>
       <c r="G21" s="15" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="C23" s="16" t="inlineStr">
         <is>
@@ -2337,14 +2331,19 @@
       </c>
       <c r="D23" s="17">
         <f>COUNTIF(F5:F21,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>de 14</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F23">
+        <f>COUNTIF(B5:B21,"?*")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
@@ -2352,6 +2351,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
@@ -2369,8 +2369,18 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G21">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2384,16 +2394,16 @@
   <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Tareas Diarias — Camarero/a</t>
@@ -2407,10 +2417,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2435,7 +2446,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2452,10 +2463,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -2481,10 +2490,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -2510,10 +2517,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -2539,10 +2544,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -2575,10 +2578,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
@@ -2604,10 +2605,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -2633,10 +2632,8 @@
       <c r="G12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
@@ -2662,10 +2659,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -2691,10 +2686,8 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -2720,10 +2713,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -2749,10 +2740,8 @@
       <c r="G16" s="11" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>11</v>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
@@ -2785,10 +2774,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
@@ -2814,10 +2801,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="20" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -2843,10 +2828,8 @@
       <c r="G20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
@@ -2872,10 +2855,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="20" t="n">
+        <v>15</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
@@ -2900,6 +2881,7 @@
       <c r="F22" s="11" t="n"/>
       <c r="G22" s="11" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="C24" s="16" t="inlineStr">
         <is>
@@ -2908,14 +2890,19 @@
       </c>
       <c r="D24" s="17">
         <f>COUNTIF(F5:F22,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>de 15</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F24">
+        <f>COUNTIF(B5:B22,"?*")</f>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
@@ -2923,6 +2910,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
@@ -2940,8 +2928,18 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G22">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F16 F17 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2955,16 +2953,16 @@
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Tareas Diarias — Auxiliar / Runner</t>
@@ -2978,10 +2976,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3006,7 +3005,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -3023,10 +3022,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -3052,10 +3049,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -3081,10 +3076,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -3110,10 +3103,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -3146,10 +3137,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
@@ -3175,10 +3164,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -3204,10 +3191,8 @@
       <c r="G12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
@@ -3233,10 +3218,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -3262,10 +3245,8 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -3298,10 +3279,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
@@ -3327,10 +3306,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -3356,10 +3333,8 @@
       <c r="G18" s="11" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
@@ -3385,10 +3360,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="20" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -3413,6 +3386,7 @@
       <c r="F20" s="11" t="n"/>
       <c r="G20" s="11" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="C22" s="16" t="inlineStr">
         <is>
@@ -3421,14 +3395,19 @@
       </c>
       <c r="D22" s="17">
         <f>COUNTIF(F5:F20,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>de 13</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F22">
+        <f>COUNTIF(B5:B20,"?*")</f>
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
@@ -3436,6 +3415,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
@@ -3453,7 +3433,17 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G20">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-cafeteria/04-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas-cafeteria/04-tareas-perfiles.xlsx
@@ -15,10 +15,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auxiliar" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Encargado'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Encargado'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Barista'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Barista'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Pastelero'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Pastelero'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Camarero'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Camarero'!$A$1:$G$28</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Auxiliar'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Auxiliar'!$A$1:$G$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -658,7 +663,7 @@
   <sheetPr>
     <tabColor rgb="00002060"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1180,8 +1185,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1190,7 +1203,7 @@
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1833,8 +1846,8 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G26">
@@ -1847,8 +1860,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1857,7 +1878,7 @@
   <sheetPr>
     <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2379,8 +2400,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2389,7 +2418,7 @@
   <sheetPr>
     <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2938,8 +2967,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2948,7 +2985,7 @@
   <sheetPr>
     <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3443,7 +3480,15 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-cafeteria/04-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas-cafeteria/04-tareas-perfiles.xlsx
@@ -15,16 +15,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auxiliar" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Encargado'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Encargado'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Encargado'!$A$1:$G$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Barista'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Barista'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Barista'!$A$1:$G$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Pastelero'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Pastelero'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Pastelero'!$A$1:$G$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Camarero'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Camarero'!$A$1:$G$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Camarero'!$A$1:$G$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Auxiliar'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Auxiliar'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Auxiliar'!$A$1:$G$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +34,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,8 +98,22 @@
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -129,6 +144,11 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -156,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -198,6 +218,50 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -575,72 +639,165 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>Tareas por Perfil Profesional — Cafetería / Brunch</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Cada pestaña contiene las tareas diarias de un perfil específico de tu cafetería.</t>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>• Entrega una copia a cada miembro del equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>• Cada perfil tiene sus tareas adaptadas a su rol</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>• El encargado supervisa que todos completen sus tareas</t>
+    <row r="6" ht="32" customHeight="1">
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
         </is>
       </c>
     </row>
     <row r="9"/>
-    <row r="10">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Formato: ☐ = tarea pendiente · ✓ = completada (escribe en columna 'Hecha')</t>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-cafeteria · info@aichef.pro</t>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala, barra café).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>▸ Estás en 04-tareas-perfiles.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="35" customHeight="1">
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-cafeteria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -665,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -715,7 +872,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -730,458 +887,523 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  APERTURA</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Abrir local y desactivar alarma</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Verificar que todo el equipo ha llegado</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Briefing: especiales, alérgenos, reservas</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Preparar fondo de caja</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Supervisar apertura de cocina, sala y barra</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Gestionar reservas y walk-ins</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Resolver incidencias con clientes</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Supervisar tiempos de espera</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Apoyar donde más se necesite (barra/sala/cocina)</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE</t>
         </is>
       </c>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="26" t="n"/>
+      <c r="E16" s="26" t="n"/>
+      <c r="F16" s="26" t="n"/>
+      <c r="G16" s="26" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Supervisar cierre de todas las áreas</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Cuadrar caja del día</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="n">
+      <c r="A19" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>Hacer pedidos para mañana</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Anotar incidencias y preparar briefing mañana</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Cerrar local: alarma, luces, gas, puertas</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
-    </row>
-    <row r="22"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
+    </row>
     <row r="23">
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D23" s="17">
-        <f>COUNTIF(F5:F21,"✓")</f>
+      <c r="A23" s="33" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="n"/>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="n"/>
+      <c r="B25" s="34" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="n"/>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D28" s="17">
+        <f>COUNTIFS(B5:B26,"?*",F5:F26,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F23">
-        <f>COUNTIF(B5:B21,"?*")</f>
+      <c r="F28">
+        <f>COUNTIF(B5:B26,"?*")-COUNTIF(F5:F26,"N/A")</f>
         <v>14.0</v>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G21">
+  <conditionalFormatting sqref="A5:G26">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1205,7 +1427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1255,7 +1477,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1270,593 +1492,658 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  APERTURA BARRA</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Encender máquina de espresso y esperar calentamiento</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>06:45</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Purgar grupos y calibrar molienda (shot de prueba)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>07:05</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Verificar stock: café, leches, siropes, té</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Preparar jarritas de leche fría</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>07:10</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Montar estación de toppings y siropes</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>07:10</t>
         </is>
       </c>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="n">
+      <c r="A11" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Preparar batch brew / café filtro</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Llenar cubitera de hielo</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>07:10</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="26" t="n"/>
+      <c r="F13" s="26" t="n"/>
+      <c r="G13" s="26" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Preparar cafés según comanda (espresso, latte, cappuccino)</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Mantener calidad constante: crema, temperatura, textura</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Limpiar portafiltro entre cada extracción</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Purgar lanza de vapor después de cada uso</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Reponer leches y café cuando baje el stock</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="n">
+      <c r="A19" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>Preparar smoothies, zumos y bebidas frías</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE BARRA</t>
         </is>
       </c>
+      <c r="B20" s="26" t="n"/>
+      <c r="C20" s="26" t="n"/>
+      <c r="D20" s="26" t="n"/>
+      <c r="E20" s="26" t="n"/>
+      <c r="F20" s="26" t="n"/>
+      <c r="G20" s="26" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Backflush máquina con pastilla de limpieza</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="n">
+      <c r="A22" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>Limpiar molinillo con cepillo</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>17:05</t>
         </is>
       </c>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="n">
+      <c r="A23" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>Lavar jarritas y utensilios</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>17:05</t>
         </is>
       </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="n">
+      <c r="A24" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>Anotar stock restante de café para pedido</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t>17:10</t>
         </is>
       </c>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="n">
+      <c r="A25" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>Limpiar superficie de barra</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="n">
+      <c r="A26" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>Apagar máquina de espresso</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
-    </row>
-    <row r="27"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="n"/>
+      <c r="B27" s="34" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="30" t="n"/>
+    </row>
     <row r="28">
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D28" s="17">
-        <f>COUNTIF(F5:F26,"✓")</f>
+      <c r="A28" s="33" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="29" t="n"/>
+      <c r="F28" s="30" t="n"/>
+      <c r="G28" s="30" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="29" t="n"/>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="30" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="29" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="30" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="30" t="n"/>
+      <c r="G31" s="30" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D33" s="17">
+        <f>COUNTIFS(B5:B31,"?*",F5:F31,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F28">
-        <f>COUNTIF(B5:B26,"?*")</f>
+      <c r="F33">
+        <f>COUNTIF(B5:B31,"?*")-COUNTIF(F5:F31,"N/A")</f>
         <v>19.0</v>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A35:G35"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A33:C33"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G26">
+  <conditionalFormatting sqref="A5:G31">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F14 F15 F16 F17 F18 F19 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F14 F15 F16 F17 F18 F19 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1880,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1930,7 +2217,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1945,458 +2232,523 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  PRODUCCIÓN</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Hornear bollería del día (croissants, muffins, magdalenas)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>06:30</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Preparar tartas del día</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>06:30</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Glasear y decorar piezas</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Preparar cookies, brownies, bizcochos</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  VITRINA Y SERVICIO</t>
         </is>
       </c>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="26" t="n"/>
+      <c r="G10" s="26" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="n">
+      <c r="A11" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Montar vitrina con producto del día</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Etiquetar: nombre, precio, alérgenos de cada pieza</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Rotar producto en vitrina (FIFO)</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Reponer vitrina durante el servicio</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Retirar producto que no esté fresco</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE</t>
         </is>
       </c>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="26" t="n"/>
+      <c r="E16" s="26" t="n"/>
+      <c r="F16" s="26" t="n"/>
+      <c r="G16" s="26" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Retirar producto de vitrina y guardar en cámara</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Etiquetar sobrantes con fecha</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="n">
+      <c r="A19" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>Limpiar zona de producción</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Anotar ventas vs producción (ajustar cantidades)</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Preparar lista de producción para mañana</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
-    </row>
-    <row r="22"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
+    </row>
     <row r="23">
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D23" s="17">
-        <f>COUNTIF(F5:F21,"✓")</f>
+      <c r="A23" s="33" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="n"/>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="n"/>
+      <c r="B25" s="34" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="n"/>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D28" s="17">
+        <f>COUNTIFS(B5:B26,"?*",F5:F26,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F23">
-        <f>COUNTIF(B5:B21,"?*")</f>
+      <c r="F28">
+        <f>COUNTIF(B5:B26,"?*")-COUNTIF(F5:F26,"N/A")</f>
         <v>14.0</v>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G21">
+  <conditionalFormatting sqref="A5:G26">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2420,7 +2772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2470,7 +2822,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -2485,485 +2837,550 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  APERTURA</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Montar mesas de tu sección</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Reponer estación: servilletas, azúcar, cubiertos</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Montar terraza si toca</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Revisar carta y especiales del día</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>07:45</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="26" t="n"/>
+      <c r="G10" s="26" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="n">
+      <c r="A11" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Recibir y acomodar clientes</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Tomar comandas (conocer alérgenos de cada plato)</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Servir bebidas y platos en tiempo</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Limpiar mesa entre clientes (rápido y discreto)</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Ofrecer postre/segunda bebida proactivamente</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Cobrar: efectivo o datáfono sin demora</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Despedir al cliente con amabilidad</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE</t>
         </is>
       </c>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="26" t="n"/>
+      <c r="G18" s="26" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="n">
+      <c r="A19" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>Desmontar mesas de tu sección</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Limpiar mesas y sillas</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Reponer estación de servicio para mañana</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="n">
+      <c r="A22" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>Recoger terraza</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
-    </row>
-    <row r="23"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+    </row>
     <row r="24">
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D24" s="17">
-        <f>COUNTIF(F5:F22,"✓")</f>
+      <c r="A24" s="33" t="n"/>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="n"/>
+      <c r="B25" s="34" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="n"/>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="n"/>
+      <c r="B27" s="34" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="30" t="n"/>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D29" s="17">
+        <f>COUNTIFS(B5:B27,"?*",F5:F27,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F24">
-        <f>COUNTIF(B5:B22,"?*")</f>
+      <c r="F29">
+        <f>COUNTIF(B5:B27,"?*")-COUNTIF(F5:F27,"N/A")</f>
         <v>15.0</v>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A28:G28"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A29:C29"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G22">
+  <conditionalFormatting sqref="A5:G27">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F16 F17 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F16 F17 F19 F20 F21 F22 F23 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2987,7 +3404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3037,7 +3454,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -3052,431 +3469,496 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  APERTURA</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Barrer y fregar suelos de sala y baños</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Limpiar cristales de entrada y ventanas</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Limpiar baños: jabón, papel, ambientador, suelo</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Baños</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Vaciar papeleras y colocar bolsas nuevas</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="26" t="n"/>
+      <c r="G10" s="26" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="n">
+      <c r="A11" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Recoger platos sucios de mesas</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Llevar comandas de cocina a sala</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Reponer cubiertos, servilletas y vasos en sala</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Apoyar en barra: lavar vasos, reponer tazas</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Mantener suelos limpios (pasar mopa si es necesario)</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE</t>
         </is>
       </c>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="26" t="n"/>
+      <c r="E16" s="26" t="n"/>
+      <c r="F16" s="26" t="n"/>
+      <c r="G16" s="26" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Office final: lavar toda la vajilla pendiente</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Barrer y fregar todos los suelos</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="n">
+      <c r="A19" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>Limpieza final de baños</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Baños</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Sacar basura y reciclaje</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-    </row>
-    <row r="21"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="n"/>
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
+    </row>
     <row r="22">
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D22" s="17">
-        <f>COUNTIF(F5:F20,"✓")</f>
+      <c r="A22" s="33" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="n"/>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="n"/>
+      <c r="B25" s="34" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D27" s="17">
+        <f>COUNTIFS(B5:B25,"?*",F5:F25,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F22">
-        <f>COUNTIF(B5:B20,"?*")</f>
+      <c r="F27">
+        <f>COUNTIF(B5:B25,"?*")-COUNTIF(F5:F25,"N/A")</f>
         <v>13.0</v>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A29:G29"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G20">
+  <conditionalFormatting sqref="A5:G25">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F17 F18 F19 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
